--- a/Selena_Master_Data_FINAL.xlsx
+++ b/Selena_Master_Data_FINAL.xlsx
@@ -478,16 +478,16 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEL-1054</t>
+          <t>SEL-1075</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Mousse Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1052861387752</v>
+        <v>1049794663708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -501,7 +501,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1054.pdf</t>
+          <t>https://selena.com/msds/SEL-1075.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -519,35 +519,35 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEL-1020</t>
+          <t>SEL-1088</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL KLEJ FIX2</t>
+          <t>Mousse Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1058682193445</v>
+        <v>1085330683268</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23 kg/m3</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1020.pdf</t>
+          <t>https://selena.com/msds/SEL-1088.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -560,35 +560,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEL-1071</t>
+          <t>SEL-1042</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1400634430439</v>
+        <v>1105727333904</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>27 kg/m3</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1071.pdf</t>
+          <t>https://selena.com/msds/SEL-1042.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -601,35 +601,35 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEL-1077</t>
+          <t>SEL-1035</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1662109815000</v>
+        <v>1159303068969</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20 kg/m3</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1077.pdf</t>
+          <t>https://selena.com/msds/SEL-1035.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -642,30 +642,30 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEL-1055</t>
+          <t>SEL-1087</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1713903214243</v>
+        <v>1248573528685</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28 kg/m3</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1055.pdf</t>
+          <t>https://selena.com/msds/SEL-1087.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -683,35 +683,35 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEL-1087</t>
+          <t>SEL-1089</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Mousse Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1742148559995</v>
+        <v>1522465041489</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>25 kg/m3</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1087.pdf</t>
+          <t>https://selena.com/msds/SEL-1089.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -724,7 +724,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEL-1029</t>
+          <t>SEL-1070</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -733,21 +733,21 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1837640308343</v>
+        <v>1628035620799</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1029.pdf</t>
+          <t>https://selena.com/msds/SEL-1070.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -765,35 +765,35 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEL-1039</t>
+          <t>SEL-1055</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL KLEJ FIX2</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>2116810251962</v>
+        <v>1683510298692</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1039.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1055.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -806,20 +806,20 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEL-1058</t>
+          <t>SEL-1015</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2238053637585</v>
+        <v>1794234331021</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1058.pdf</t>
+          <t>https://selena.com/msds/SEL-1015.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -847,30 +847,30 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEL-1091</t>
+          <t>SEL-1067</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Mousse Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2423614829520</v>
+        <v>1963951178364</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>24 kg/m3</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1091.pdf</t>
+          <t>https://selena.com/msds/SEL-1067.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -888,16 +888,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEL-1059</t>
+          <t>SEL-1014</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>TYTAN PROFESSIONAL SILIKON SANITARNY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2443394692443</v>
+        <v>2052524886138</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -906,12 +906,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1059.pdf</t>
+          <t>https://selena.com/msds/SEL-1014.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -929,35 +929,35 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEL-1033</t>
+          <t>SEL-1065</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Mousse Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2474868174150</v>
+        <v>2101843653145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>25 kg/m3</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1033.pdf</t>
+          <t>https://selena.com/msds/SEL-1065.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -970,35 +970,35 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEL-1028</t>
+          <t>SEL-1063</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2541921310761</v>
+        <v>2132634819632</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1028.pdf</t>
+          <t>https://selena.com/msds/SEL-1063.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1011,30 +1011,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL-1099</t>
+          <t>SEL-1009</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2618558137840</v>
+        <v>2183419236281</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1099.pdf</t>
+          <t>https://selena.com/msds/SEL-1009.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1052,30 +1052,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEL-1081</t>
+          <t>SEL-1046</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2749732278057</v>
+        <v>2254382474668</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>20 kg/m3</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1081.pdf</t>
+          <t>https://selena.com/msds/SEL-1046.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1093,35 +1093,35 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEL-1083</t>
+          <t>SEL-1048</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ARTELIT PIANA 65</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2833514552515</v>
+        <v>2259602564922</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1083.pdf</t>
+          <t>https://selena.com/msds/SEL-1048.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1134,35 +1134,35 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEL-1045</t>
+          <t>SEL-1062</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>ARTELIT PIANA 65</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2853343938704</v>
+        <v>2524834292213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1045.pdf</t>
+          <t>https://selena.com/msds/SEL-1062.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1175,35 +1175,35 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEL-1032</t>
+          <t>SEL-1080</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3050134715475</v>
+        <v>2555872688129</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1032.pdf</t>
+          <t>https://selena.com/msds/SEL-1080.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1216,16 +1216,16 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEL-1042</t>
+          <t>SEL-1059</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>3065589789922</v>
+        <v>2680924202250</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1234,17 +1234,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1042.pdf</t>
+          <t>https://selena.com/msds/SEL-1059.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1257,35 +1257,35 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEL-1019</t>
+          <t>SEL-1036</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3188569644058</v>
+        <v>2744460982750</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1019.pdf</t>
+          <t>https://selena.com/msds/SEL-1036.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1298,7 +1298,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEL-1097</t>
+          <t>SEL-1090</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1307,7 +1307,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3287800277732</v>
+        <v>2873432149063</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>23 kg/m3</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1097.pdf</t>
+          <t>https://selena.com/msds/SEL-1090.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1339,35 +1339,35 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEL-1037</t>
+          <t>SEL-1002</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Mousse Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>3331112155758</v>
+        <v>2893065528455</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1037.pdf</t>
+          <t>https://selena.com/msds/SEL-1002.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1380,35 +1380,35 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEL-1068</t>
+          <t>SEL-1018</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>QUILOSA PIANA 65</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>3334083932806</v>
+        <v>2927062980266</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1068.pdf</t>
+          <t>https://selena.com/msds/SEL-1018.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1421,30 +1421,30 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEL-1049</t>
+          <t>SEL-1022</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL KLEJ FIX2</t>
+          <t>Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3356783066634</v>
+        <v>3014909833096</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1049.pdf</t>
+          <t>https://selena.com/msds/SEL-1022.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1462,35 +1462,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEL-1038</t>
+          <t>SEL-1027</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Mousse Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3361667826705</v>
+        <v>3018667068236</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1038.pdf</t>
+          <t>https://selena.com/msds/SEL-1027.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1503,16 +1503,16 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEL-1031</t>
+          <t>SEL-1093</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3366858305704</v>
+        <v>3124395641265</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1031.pdf</t>
+          <t>https://selena.com/msds/SEL-1093.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1544,30 +1544,30 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEL-1046</t>
+          <t>SEL-1064</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>QUILOSA PIANA 65</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3530186665272</v>
+        <v>3210042484187</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1046.pdf</t>
+          <t>https://selena.com/msds/SEL-1064.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1585,35 +1585,35 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEL-1017</t>
+          <t>SEL-1086</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t>QUILOSA PIANA 65</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3714633034243</v>
+        <v>3370951422097</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1017.pdf</t>
+          <t>https://selena.com/msds/SEL-1086.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1626,35 +1626,35 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEL-1016</t>
+          <t>SEL-1038</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mousse Artelit Klej Fix2</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3952031874881</v>
+        <v>3399061348419</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>30 kg/m3</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1016.pdf</t>
+          <t>https://selena.com/msds/SEL-1038.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -1667,35 +1667,35 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEL-1041</t>
+          <t>SEL-1071</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>4216677327882</v>
+        <v>3503560136682</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1041.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1071.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -1708,16 +1708,16 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEL-1004</t>
+          <t>SEL-1016</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>QUILOSA PIANA 65</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4464281762099</v>
+        <v>3607094219856</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -1726,17 +1726,17 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1004.pdf</t>
+          <t>https://selena.com/msds/SEL-1016.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1749,35 +1749,35 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEL-1089</t>
+          <t>SEL-1097</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>ARTELIT SILIKON SANITARNY</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>4510330412869</v>
+        <v>3828039096400</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1089.pdf</t>
+          <t>https://selena.com/msds/SEL-1097.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1790,30 +1790,30 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEL-1069</t>
+          <t>SEL-1057</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4709523457654</v>
+        <v>4128268616743</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>30 kg/m3</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1069.pdf</t>
+          <t>https://selena.com/msds/SEL-1057.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1831,35 +1831,35 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEL-1047</t>
+          <t>SEL-1095</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4725877341208</v>
+        <v>4202042993337</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>25 kg/m3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1047.pdf</t>
+          <t>https://selena.com/msds/SEL-1095.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -1872,16 +1872,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEL-1044</t>
+          <t>SEL-1011</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Mousse Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4742503550712</v>
+        <v>4236057267565</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1890,12 +1890,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>26 kg/m3</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1044.pdf</t>
+          <t>https://selena.com/msds/SEL-1011.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -1913,35 +1913,35 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEL-1090</t>
+          <t>SEL-1052</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>Mousse Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4753403689072</v>
+        <v>4260718493008</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30 kg/m3</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1090.pdf</t>
+          <t>https://selena.com/msds/SEL-1052.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -1954,35 +1954,35 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEL-1053</t>
+          <t>SEL-1081</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4772614139806</v>
+        <v>4345790925489</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1053.pdf</t>
+          <t>https://selena.com/msds/SEL-1081.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -1995,30 +1995,30 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEL-1026</t>
+          <t>SEL-1054</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4876766323931</v>
+        <v>4410489689561</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>29 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1026.pdf</t>
+          <t>https://selena.com/msds/SEL-1054.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -2036,35 +2036,35 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEL-1067</t>
+          <t>SEL-1020</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5134123813034</v>
+        <v>4463282966117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1067.pdf</t>
+          <t>https://selena.com/msds/SEL-1020.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -2077,30 +2077,30 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEL-1061</t>
+          <t>SEL-1098</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>Mousse Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>5149976668305</v>
+        <v>4485357398066</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>24 kg/m3</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1061.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1098.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2118,30 +2118,30 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEL-1057</t>
+          <t>SEL-1013</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>5228798387520</v>
+        <v>4760793164326</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1057.pdf</t>
+          <t>https://selena.com/msds/SEL-1013.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2159,35 +2159,35 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEL-1063</t>
+          <t>SEL-1037</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>ARTELIT KLEJ FIX2</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>5275353238340</v>
+        <v>4800217003895</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1063.pdf</t>
+          <t>https://selena.com/msds/SEL-1037.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -2200,30 +2200,30 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEL-1010</t>
+          <t>SEL-1083</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>5378173892334</v>
+        <v>4805814994799</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1010.pdf</t>
+          <t>https://selena.com/msds/SEL-1083.pdf</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2241,16 +2241,16 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEL-1056</t>
+          <t>SEL-1033</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>ARTELIT PIANA 65</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5551603476820</v>
+        <v>4839616754629</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -2259,12 +2259,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1056.pdf</t>
+          <t>https://selena.com/msds/SEL-1033.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2282,16 +2282,16 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEL-1064</t>
+          <t>SEL-1024</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5665322955372</v>
+        <v>4924751211578</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -2300,12 +2300,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>27 kg/m3</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1064.pdf</t>
+          <t>https://selena.com/msds/SEL-1024.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2323,30 +2323,30 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEL-1095</t>
+          <t>SEL-1060</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5712161193508</v>
+        <v>5110033164827</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1095.pdf</t>
+          <t>https://selena.com/msds/SEL-1060.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2364,30 +2364,30 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEL-1060</t>
+          <t>SEL-1072</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5755215257448</v>
+        <v>5319581949455</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>29 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1060.pdf</t>
+          <t>https://selena.com/msds/SEL-1072.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -2405,35 +2405,35 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEL-1030</t>
+          <t>SEL-1068</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5805160588911</v>
+        <v>5582183398205</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>22 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1030.pdf</t>
+          <t>https://selena.com/msds/SEL-1068.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H49" t="b">
@@ -2446,16 +2446,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEL-1094</t>
+          <t>SEL-1021</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Mousse Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5810562694186</v>
+        <v>5719895208452</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2464,17 +2464,17 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>27 kg/m3</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1094.pdf</t>
+          <t>https://selena.com/msds/SEL-1021.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H50" t="b">
@@ -2487,30 +2487,30 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEL-1027</t>
+          <t>SEL-1078</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5830751435166</v>
+        <v>5861090712118</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1027.pdf</t>
+          <t>https://selena.com/msds/SEL-1078.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2533,25 +2533,25 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Mousse Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5855686951890</v>
+        <v>5879050548824</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1085.pdf</t>
+          <t>https://selena.com/msds/SEL-1085.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2569,20 +2569,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEL-1093</t>
+          <t>SEL-1050</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL SILIKON SANITARNY</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>5880454997974</v>
+        <v>6093257624840</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1093.pdf</t>
+          <t>https://selena.com/msds/SEL-1050.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H53" t="b">
@@ -2610,35 +2610,35 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEL-1086</t>
+          <t>SEL-1056</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>QUILOSA KLEJ FIX2</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6046014870937</v>
+        <v>6128870282327</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1086.pdf</t>
+          <t>https://selena.com/msds/SEL-1056.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H54" t="b">
@@ -2651,35 +2651,35 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEL-1022</t>
+          <t>SEL-1091</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>QUILOSA SILIKON SANITARNY</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6294075288079</v>
+        <v>6301242150038</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>28</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1022.pdf</t>
+          <t>https://selena.com/msds/SEL-1091.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H55" t="b">
@@ -2692,7 +2692,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEL-1011</t>
+          <t>SEL-1061</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6344133179342</v>
+        <v>6359727781882</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2710,17 +2710,17 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1011.pdf</t>
+          <t>https://selena.com/msds/SEL-1061.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H56" t="b">
@@ -2733,16 +2733,16 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEL-1036</t>
+          <t>SEL-1099</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>ARTELIT KLEJ FIX2</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6431429645315</v>
+        <v>6372752264093</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2751,12 +2751,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1036.pdf</t>
+          <t>https://selena.com/msds/SEL-1099.pdf</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2774,16 +2774,16 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEL-1043</t>
+          <t>SEL-1029</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6581815589425</v>
+        <v>6399406808684</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2792,17 +2792,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1043.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1029.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H58" t="b">
@@ -2815,35 +2815,35 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEL-1051</t>
+          <t>SEL-1023</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t>QUILOSA SILIKON SANITARNY</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6649578408106</v>
+        <v>6464571224759</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>29 kg/m3</t>
+          <t>21</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1051.pdf</t>
+          <t>https://selena.com/msds/SEL-1023.pdf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -2856,35 +2856,35 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEL-1076</t>
+          <t>SEL-1096</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL KLEJ FIX2</t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6776967111397</v>
+        <v>6530875644106</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>21 kg/m3</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1076.pdf</t>
+          <t>https://selena.com/msds/SEL-1096.pdf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H60" t="b">
@@ -2897,35 +2897,35 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEL-1080</t>
+          <t>SEL-1043</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Mousse Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6781413762218</v>
+        <v>6578536710611</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28 kg/m3</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1080.pdf</t>
+          <t>https://selena.com/msds/SEL-1043.pdf</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H61" t="b">
@@ -2938,35 +2938,35 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEL-1082</t>
+          <t>SEL-1069</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL SILIKON SANITARNY</t>
+          <t>Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6820594845002</v>
+        <v>6613038399494</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1082.pdf</t>
+          <t>https://selena.com/msds/SEL-1069.pdf</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H62" t="b">
@@ -2979,30 +2979,30 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEL-1073</t>
+          <t>SEL-1026</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6935206188161</v>
+        <v>6846915783781</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1073.pdf</t>
+          <t>https://selena.com/msds/SEL-1026.pdf</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3020,20 +3020,20 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEL-1075</t>
+          <t>SEL-1030</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6966242242365</v>
+        <v>6903577573831</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -3043,12 +3043,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1075.pdf</t>
+          <t>https://selena.com/msds/SEL-1030.pdf</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H64" t="b">
@@ -3061,35 +3061,35 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEL-1052</t>
+          <t>SEL-1092</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6968733837222</v>
+        <v>7096109238311</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1052.pdf</t>
+          <t>https://selena.com/msds/SEL-1092.pdf</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H65" t="b">
@@ -3102,16 +3102,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEL-1062</t>
+          <t>SEL-1066</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>QUILOSA PIANA 65</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7057236931336</v>
+        <v>7153037182316</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -3125,12 +3125,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1062.pdf</t>
+          <t>https://selena.com/msds/SEL-1066.pdf</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -3143,16 +3143,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEL-1079</t>
+          <t>SEL-1051</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>TYTAN PROFESSIONAL PIANA 65</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7125641250587</v>
+        <v>7270011574069</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3161,17 +3161,17 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1079.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1051.pdf</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H67" t="b">
@@ -3184,16 +3184,16 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEL-1018</t>
+          <t>SEL-1039</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7163018941571</v>
+        <v>7351914924233</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3202,17 +3202,17 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1018.pdf</t>
+          <t>https://selena.com/msds/SEL-1039.pdf</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H68" t="b">
@@ -3225,16 +3225,16 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEL-1088</t>
+          <t>SEL-1077</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Artelit Silikon Sanitarny</t>
+          <t>QUILOSA PIANA 65</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7227672436686</v>
+        <v>7428925382389</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -3243,17 +3243,17 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1088.pdf</t>
+          <t>https://selena.com/msds/SEL-1077.pdf</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H69" t="b">
@@ -3266,30 +3266,30 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEL-1024</t>
+          <t>SEL-1082</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7467004618155</v>
+        <v>7452563170336</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1024.pdf</t>
+          <t>https://selena.com/msds/SEL-1082.pdf</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -3307,35 +3307,35 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEL-1096</t>
+          <t>SEL-1044</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Artelit Klej Fix2</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7940081444587</v>
+        <v>7649285435337</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>22</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1096.pdf</t>
+          <t>https://selena.com/msds/SEL-1044.pdf</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H71" t="b">
@@ -3348,35 +3348,35 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEL-1015</t>
+          <t>SEL-1053</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Mousse Quilosa Klej Fix2</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8022669861656</v>
+        <v>7659662268714</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>20 kg/m3</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1015.pdf</t>
+          <t>https://selena.com/msds/SEL-1053.pdf</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H72" t="b">
@@ -3389,16 +3389,16 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEL-1050</t>
+          <t>SEL-1045</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mousse Artelit Klej Fix2</t>
+          <t>Mousse Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8057008990008</v>
+        <v>7937353461559</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>23 kg/m3</t>
+          <t>21 kg/m3</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1050.pdf</t>
+          <t>https://selena.com/msds/SEL-1045.pdf</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -3430,35 +3430,35 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEL-1025</t>
+          <t>SEL-1041</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>Tytan Professional Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8344590585850</v>
+        <v>7975992297811</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1025.pdf</t>
+          <t>https://selena.com/msds/SEL-1041.pdf</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H74" t="b">
@@ -3471,35 +3471,35 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEL-1084</t>
+          <t>SEL-1028</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8352411674492</v>
+        <v>8088745651215</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>brak</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1084.pdf</t>
+          <t>https://selena.com/msds/SEL-1028.pdf</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H75" t="b">
@@ -3512,35 +3512,35 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEL-1074</t>
+          <t>SEL-1017</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Silikon Sanitarny</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8482267920027</v>
+        <v>8263639919343</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>24 kg/m3</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1074.pdf</t>
+          <t>https://selena.com/msds/SEL-1017.pdf</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -3553,35 +3553,35 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEL-1098</t>
+          <t>SEL-1094</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Mousse Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8522059501608</v>
+        <v>8271954408988</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>29 kg/m3</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1098.pdf</t>
+          <t>https://selena.com/msds/SEL-1094.pdf</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H77" t="b">
@@ -3594,35 +3594,35 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEL-1072</t>
+          <t>SEL-1025</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>Mousse Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8643019841877</v>
+        <v>8498444065138</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>23 kg/m3</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1072.pdf</t>
+          <t>https://selena.com/msds/SEL-1025.pdf</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H78" t="b">
@@ -3635,35 +3635,35 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEL-1048</t>
+          <t>SEL-1040</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Mousse Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8650771138981</v>
+        <v>8653589174947</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>20 kg/m3</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1048.pdf</t>
+          <t>https://selena.com/msds/SEL-1040.pdf</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H79" t="b">
@@ -3676,30 +3676,30 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEL-1035</t>
+          <t>SEL-1010</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Mousse Artelit Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8652016489943</v>
+        <v>8752167857609</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>27 kg/m3</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1035.pdf</t>
+          <t>https://selena.com/msds/SEL-1010.pdf</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -3717,35 +3717,35 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEL-1021</t>
+          <t>SEL-1049</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ARTELIT PIANA 65</t>
+          <t>Mousse Artelit Piana 65</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8715117804382</v>
+        <v>8837124382189</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>26 kg/m3</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1021.pdf</t>
+          <t>https://selena.com/msds/SEL-1049.pdf</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H81" t="b">
@@ -3758,35 +3758,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEL-1034</t>
+          <t>SEL-1058</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>QUILOSA KLEJ FIX2</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>8719308305932</v>
+        <v>9081504056920</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>25</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1034.pdf</t>
+          <t>https://selena.com/msds/SEL-1058.pdf</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H82" t="b">
@@ -3799,16 +3799,16 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SEL-1040</t>
+          <t>SEL-1074</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>8802480519614</v>
+        <v>9191829276099</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3817,12 +3817,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>27</t>
+          <t>26</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1040.pdf</t>
+          <t>https://selena.com/msds/SEL-1074.pdf</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -3840,16 +3840,16 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SEL-1012</t>
+          <t>SEL-1034</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>8874326971831</v>
+        <v>9319236221700</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -3858,17 +3858,17 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>20</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1012.pdf</t>
+          <t>https://selena.com/msds/SEL-1034.pdf</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -3881,35 +3881,35 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SEL-1023</t>
+          <t>SEL-1031</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>QUILOSA KLEJ FIX2</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9186185848502</v>
+        <v>9372306162861</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1023.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1031.pdf</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -3922,30 +3922,30 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SEL-1078</t>
+          <t>SEL-1076</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>Quilosa Silikon Sanitarny</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9300943099236</v>
+        <v>9403942692974</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>27</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1078.pdf</t>
+          <t>https://selena.com/msds/SEL-1076.pdf</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3963,35 +3963,35 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SEL-1092</t>
+          <t>SEL-1032</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Mousse Artelit Klej Fix2</t>
+          <t>TYTAN PROFESSIONAL PIANA 65</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9321360945847</v>
+        <v>9426646806022</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>28 kg/m3</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1092.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1032.pdf</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H87" t="b">
@@ -4004,30 +4004,30 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SEL-1065</t>
+          <t>SEL-1047</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>Tytan Professional Klej Fix2</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9487213773352</v>
+        <v>9500885725153</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>29</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1065.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1047.pdf</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4045,16 +4045,16 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SEL-1066</t>
+          <t>SEL-1084</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>ARTELIT SILIKON SANITARNY</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9518883419314</v>
+        <v>9758501126444</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -4063,17 +4063,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>24</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1066.pdf</t>
+          <t>https://selena.com/msds/SEL-1084.pdf</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H89" t="b">
@@ -4086,35 +4086,35 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SEL-1013</t>
+          <t>SEL-1079</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL KLEJ FIX2</t>
+          <t>TYTAN PROFESSIONAL SILIKON SANITARNY</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9782657883637</v>
+        <v>9851835131072</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>29</t>
+          <t>30</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1013.pdf</t>
+          <t>https://selena.com/msds/SEL-1079.pdf</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H90" t="b">
@@ -4127,35 +4127,35 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SEL-1070</t>
+          <t>SEL-1073</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>QUILOSA SILIKON SANITARNY</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9954571394313</v>
+        <v>9890039511679</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>23</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1070.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-1073.pdf</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H91" t="b">

--- a/Selena_Master_Data_FINAL.xlsx
+++ b/Selena_Master_Data_FINAL.xlsx
@@ -478,30 +478,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEL-1075</t>
+          <t>SEL-2048</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1049794663708</v>
+        <v>1022373185644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>22 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>28</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1075.pdf</t>
+          <t>https://selena.com/msds/SEL-2048.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -519,35 +517,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEL-1088</t>
+          <t>SEL-2044</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1085330683268</v>
+        <v>1092684287836</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>23 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>28</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1088.pdf</t>
+          <t>https://selena.com/msds/SEL-2044.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -560,35 +556,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEL-1042</t>
+          <t>SEL-2089</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1105727333904</v>
+        <v>1143805552958</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>27 kg/m3</t>
-        </is>
+      <c r="E4" t="n">
+        <v>28</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1042.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2089.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -601,30 +595,28 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEL-1035</t>
+          <t>SEL-2010</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1159303068969</v>
+        <v>1204110767442</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>28</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1035.pdf</t>
+          <t>https://selena.com/msds/SEL-2010.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -642,35 +634,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEL-1087</t>
+          <t>SEL-2011</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1248573528685</v>
+        <v>1431313708027</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>28 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>28</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1087.pdf</t>
+          <t>https://selena.com/msds/SEL-2011.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -683,35 +673,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEL-1089</t>
+          <t>SEL-2038</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1522465041489</v>
+        <v>1490743066339</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>25 kg/m3</t>
-        </is>
+      <c r="E7" t="n">
+        <v>28</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1089.pdf</t>
+          <t>https://selena.com/msds/SEL-2038.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -724,35 +712,33 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEL-1070</t>
+          <t>SEL-1016</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1628035620799</v>
+        <v>1677703171119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>25</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1070.pdf</t>
+          <t>https://selena.com/msds/SEL-1016.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H8" t="b">
@@ -765,35 +751,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEL-1055</t>
+          <t>SEL-2060</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1683510298692</v>
+        <v>1724818207492</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>28</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1055.pdf</t>
+          <t>https://selena.com/msds/SEL-2060.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -806,30 +790,28 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEL-1015</t>
+          <t>SEL-2085</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Artelit Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1794234331021</v>
+        <v>1749267817447</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="E10" t="n">
+        <v>28</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1015.pdf</t>
+          <t>https://selena.com/msds/SEL-2085.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -847,35 +829,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEL-1067</t>
+          <t>SEL-2063</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1963951178364</v>
+        <v>1764984288667</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>24 kg/m3</t>
-        </is>
+      <c r="E11" t="n">
+        <v>28</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1067.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2063.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -888,35 +868,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEL-1014</t>
+          <t>SEL-2047</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL SILIKON SANITARNY</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2052524886138</v>
+        <v>1791439611947</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>28</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1014.pdf</t>
+          <t>https://selena.com/msds/SEL-2047.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -929,30 +907,28 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEL-1065</t>
+          <t>SEL-1008</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2101843653145</v>
+        <v>1791623521699</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>25 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>25</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1065.pdf</t>
+          <t>https://selena.com/msds/SEL-1008.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -970,35 +946,33 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEL-1063</t>
+          <t>SEL-2070</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>2132634819632</v>
+        <v>1832833357240</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>28</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1063.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2070.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -1011,30 +985,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL-1009</t>
+          <t>SEL-1000</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2183419236281</v>
+        <v>1936449043351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>25</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1009.pdf</t>
+          <t>https://selena.com/msds/SEL-1000.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1052,30 +1024,28 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEL-1046</t>
+          <t>SEL-1014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2254382474668</v>
+        <v>2097253614102</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>20 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>25</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1046.pdf</t>
+          <t>https://selena.com/msds/SEL-1014.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1093,35 +1063,33 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEL-1048</t>
+          <t>SEL-2068</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2259602564922</v>
+        <v>2343285886804</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>28</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1048.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2068.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1134,30 +1102,28 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEL-1062</t>
+          <t>SEL-2021</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2524834292213</v>
+        <v>2422334086189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="E18" t="n">
+        <v>28</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1062.pdf</t>
+          <t>https://selena.com/msds/SEL-2021.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1175,35 +1141,33 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEL-1080</t>
+          <t>SEL-2045</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2555872688129</v>
+        <v>2456811561472</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>28</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1080.pdf</t>
+          <t>https://selena.com/msds/SEL-2045.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1216,30 +1180,28 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SEL-1059</t>
+          <t>SEL-2018</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2680924202250</v>
+        <v>2460088159013</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E20" t="n">
+        <v>28</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1059.pdf</t>
+          <t>https://selena.com/msds/SEL-2018.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1257,30 +1219,28 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEL-1036</t>
+          <t>SEL-2082</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2744460982750</v>
+        <v>2576561330723</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="E21" t="n">
+        <v>28</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1036.pdf</t>
+          <t>https://selena.com/msds/SEL-2082.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1298,30 +1258,28 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEL-1090</t>
+          <t>SEL-2034</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2873432149063</v>
+        <v>2670068131331</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>23 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>28</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1090.pdf</t>
+          <t>https://selena.com/msds/SEL-2034.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1339,35 +1297,33 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEL-1002</t>
+          <t>SEL-2024</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2893065528455</v>
+        <v>2684136327243</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>21 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>28</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1002.pdf</t>
+          <t>https://selena.com/msds/SEL-2024.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1380,35 +1336,33 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEL-1018</t>
+          <t>SEL-2029</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2927062980266</v>
+        <v>2734724082384</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="E24" t="n">
+        <v>28</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1018.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2029.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1421,35 +1375,33 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEL-1022</t>
+          <t>SEL-2076</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3014909833096</v>
+        <v>2745092225361</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>28</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1022.pdf</t>
+          <t>https://selena.com/msds/SEL-2076.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1462,30 +1414,28 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEL-1027</t>
+          <t>SEL-2036</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3018667068236</v>
+        <v>3118512000486</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>21 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>28</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1027.pdf</t>
+          <t>https://selena.com/msds/SEL-2036.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1503,35 +1453,33 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEL-1093</t>
+          <t>SEL-2053</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3124395641265</v>
+        <v>3197400489411</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="E27" t="n">
+        <v>28</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1093.pdf</t>
+          <t>https://selena.com/msds/SEL-2053.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1544,35 +1492,33 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEL-1064</t>
+          <t>SEL-2083</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3210042484187</v>
+        <v>3337387430454</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>28</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1064.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2083.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H28" t="b">
@@ -1585,30 +1531,28 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEL-1086</t>
+          <t>SEL-2051</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3370951422097</v>
+        <v>3441744655831</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="E29" t="n">
+        <v>28</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1086.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2051.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1626,35 +1570,33 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEL-1038</t>
+          <t>SEL-2032</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3399061348419</v>
+        <v>3614691233930</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>28</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1038.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2032.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -1667,35 +1609,33 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEL-1071</t>
+          <t>SEL-2065</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3503560136682</v>
+        <v>3726173435905</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>28</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1071.pdf</t>
+          <t>https://selena.com/msds/SEL-2065.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -1708,35 +1648,33 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEL-1016</t>
+          <t>SEL-2057</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3607094219856</v>
+        <v>3779377392144</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>28</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1016.pdf</t>
+          <t>https://selena.com/msds/SEL-2057.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1749,35 +1687,33 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEL-1097</t>
+          <t>SEL-2013</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3828039096400</v>
+        <v>3795160531739</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+      <c r="E33" t="n">
+        <v>28</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1097.pdf</t>
+          <t>https://selena.com/msds/SEL-2013.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1790,35 +1726,33 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEL-1057</t>
+          <t>SEL-2056</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4128268616743</v>
+        <v>3925124752011</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>30 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>28</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1057.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2056.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -1831,35 +1765,33 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEL-1095</t>
+          <t>SEL-2028</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4202042993337</v>
+        <v>3934611066963</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>28</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1095.pdf</t>
+          <t>https://selena.com/msds/SEL-2028.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -1872,35 +1804,33 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEL-1011</t>
+          <t>SEL-2052</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4236057267565</v>
+        <v>3989592443173</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>26 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>28</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1011.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2052.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -1913,35 +1843,33 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEL-1052</t>
+          <t>SEL-2022</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>4260718493008</v>
+        <v>3989697366878</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>30 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>28</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1052.pdf</t>
+          <t>https://selena.com/msds/SEL-2022.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -1954,30 +1882,28 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEL-1081</t>
+          <t>SEL-2026</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4345790925489</v>
+        <v>4102374178177</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>28</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1081.pdf</t>
+          <t>https://selena.com/msds/SEL-2026.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1995,35 +1921,33 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEL-1054</t>
+          <t>SEL-2020</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4410489689561</v>
+        <v>4380545170318</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>28</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1054.pdf</t>
+          <t>https://selena.com/msds/SEL-2020.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -2036,35 +1960,33 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEL-1020</t>
+          <t>SEL-2080</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4463282966117</v>
+        <v>4465563544233</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E40" t="n">
+        <v>28</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1020.pdf</t>
+          <t>https://selena.com/msds/SEL-2080.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -2077,30 +1999,28 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEL-1098</t>
+          <t>SEL-2015</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4485357398066</v>
+        <v>4513340336745</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>24 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>28</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1098.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2015.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2118,35 +2038,33 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEL-1013</t>
+          <t>SEL-2027</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4760793164326</v>
+        <v>4573368667749</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>28</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1013.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2027.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -2159,30 +2077,28 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEL-1037</t>
+          <t>SEL-2042</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>ARTELIT KLEJ FIX2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4800217003895</v>
+        <v>4684061093349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>28</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1037.pdf</t>
+          <t>https://selena.com/msds/SEL-2042.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -2200,35 +2116,33 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEL-1083</t>
+          <t>SEL-2067</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4805814994799</v>
+        <v>4992598590558</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>28</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1083.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2067.pdf</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H44" t="b">
@@ -2241,35 +2155,33 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEL-1033</t>
+          <t>SEL-2033</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>ARTELIT PIANA 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>4839616754629</v>
+        <v>5029944637928</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>28</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1033.pdf</t>
+          <t>https://selena.com/msds/SEL-2033.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -2282,35 +2194,33 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEL-1024</t>
+          <t>SEL-2084</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4924751211578</v>
+        <v>5093439265601</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>21 kg/m3</t>
-        </is>
+      <c r="E46" t="n">
+        <v>28</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1024.pdf</t>
+          <t>https://selena.com/msds/SEL-2084.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H46" t="b">
@@ -2323,30 +2233,28 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEL-1060</t>
+          <t>SEL-2046</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5110033164827</v>
+        <v>5137387139033</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>28</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1060.pdf</t>
+          <t>https://selena.com/msds/SEL-2046.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2364,35 +2272,33 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEL-1072</t>
+          <t>SEL-2016</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5319581949455</v>
+        <v>5213263670202</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>28</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1072.pdf</t>
+          <t>https://selena.com/msds/SEL-2016.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H48" t="b">
@@ -2405,30 +2311,28 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEL-1068</t>
+          <t>SEL-2077</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5582183398205</v>
+        <v>5303184181413</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>28</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1068.pdf</t>
+          <t>https://selena.com/msds/SEL-2077.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2446,35 +2350,33 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEL-1021</t>
+          <t>SEL-2081</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5719895208452</v>
+        <v>5726340673312</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>27 kg/m3</t>
-        </is>
+      <c r="E50" t="n">
+        <v>28</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1021.pdf</t>
+          <t>https://selena.com/msds/SEL-2081.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H50" t="b">
@@ -2487,30 +2389,28 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEL-1078</t>
+          <t>SEL-2055</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5861090712118</v>
+        <v>5926862184008</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="E51" t="n">
+        <v>28</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1078.pdf</t>
+          <t>https://selena.com/msds/SEL-2055.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -2528,35 +2428,33 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEL-1085</t>
+          <t>SEL-2019</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5879050548824</v>
+        <v>5988931325193</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>21 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>28</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1085.pdf</t>
+          <t>https://selena.com/msds/SEL-2019.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -2569,35 +2467,33 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEL-1050</t>
+          <t>SEL-2023</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6093257624840</v>
+        <v>6023232068164</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>28</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1050.pdf</t>
+          <t>https://selena.com/msds/SEL-2023.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H53" t="b">
@@ -2610,30 +2506,28 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEL-1056</t>
+          <t>SEL-2050</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6128870282327</v>
+        <v>6173511481463</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>28</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1056.pdf</t>
+          <t>https://selena.com/msds/SEL-2050.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2651,30 +2545,28 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEL-1091</t>
+          <t>SEL-2035</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6301242150038</v>
+        <v>6262788108202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>28</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1091.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2035.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2692,35 +2584,33 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEL-1061</t>
+          <t>SEL-2061</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6359727781882</v>
+        <v>6311693356798</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>28</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1061.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2061.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H56" t="b">
@@ -2733,35 +2623,33 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEL-1099</t>
+          <t>SEL-2014</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6372752264093</v>
+        <v>6446862466631</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="E57" t="n">
+        <v>28</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1099.pdf</t>
+          <t>https://selena.com/msds/SEL-2014.pdf</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H57" t="b">
@@ -2774,30 +2662,28 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEL-1029</t>
+          <t>SEL-2072</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6399406808684</v>
+        <v>6450486585484</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>28</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1029.pdf</t>
+          <t>https://selena.com/msds/SEL-2072.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2815,35 +2701,33 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEL-1023</t>
+          <t>SEL-2066</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6464571224759</v>
+        <v>6580952323893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
+      <c r="E59" t="n">
+        <v>28</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1023.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2066.pdf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -2856,30 +2740,28 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEL-1096</t>
+          <t>SEL-2059</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6530875644106</v>
+        <v>6618629275523</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="E60" t="n">
+        <v>28</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1096.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2059.pdf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2897,35 +2779,33 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEL-1043</t>
+          <t>SEL-2069</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6578536710611</v>
+        <v>6672228217380</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>28 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>28</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1043.pdf</t>
+          <t>https://selena.com/msds/SEL-2069.pdf</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H61" t="b">
@@ -2938,35 +2818,33 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEL-1069</t>
+          <t>SEL-2049</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Quilosa Klej Fix2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6613038399494</v>
+        <v>6715757390739</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>28</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1069.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2049.pdf</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H62" t="b">
@@ -2979,30 +2857,28 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEL-1026</t>
+          <t>SEL-2086</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6846915783781</v>
+        <v>6718682523145</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>28</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1026.pdf</t>
+          <t>https://selena.com/msds/SEL-2086.pdf</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
@@ -3020,35 +2896,33 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEL-1030</t>
+          <t>SEL-1006</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6903577573831</v>
+        <v>6762341715348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="E64" t="n">
+        <v>25</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1030.pdf</t>
+          <t>https://selena.com/msds/SEL-1006.pdf</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H64" t="b">
@@ -3061,35 +2935,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEL-1092</t>
+          <t>SEL-1012</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>7096109238311</v>
+        <v>6855268434259</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+      <c r="E65" t="n">
+        <v>25</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1092.pdf</t>
+          <t>https://selena.com/msds/SEL-1012.pdf</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H65" t="b">
@@ -3102,35 +2974,33 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEL-1066</t>
+          <t>SEL-2054</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7153037182316</v>
+        <v>7292520518128</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="E66" t="n">
+        <v>28</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1066.pdf</t>
+          <t>https://selena.com/msds/SEL-2054.pdf</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -3143,35 +3013,33 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEL-1051</t>
+          <t>SEL-1010</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7270011574069</v>
+        <v>7450121326874</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="E67" t="n">
+        <v>25</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1051.pdf</t>
+          <t>https://selena.com/msds/SEL-1010.pdf</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H67" t="b">
@@ -3184,35 +3052,33 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEL-1039</t>
+          <t>SEL-2079</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7351914924233</v>
+        <v>7528580919923</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>28</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1039.pdf</t>
+          <t>https://selena.com/msds/SEL-2079.pdf</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H68" t="b">
@@ -3225,30 +3091,28 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEL-1077</t>
+          <t>SEL-2074</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>QUILOSA PIANA 65</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7428925382389</v>
+        <v>7683489560336</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="E69" t="n">
+        <v>28</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1077.pdf</t>
+          <t>https://selena.com/msds/SEL-2074.pdf</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -3266,35 +3130,33 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEL-1082</t>
+          <t>SEL-2088</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7452563170336</v>
+        <v>7856245875389</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>28</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1082.pdf</t>
+          <t>https://selena.com/msds/SEL-2088.pdf</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H70" t="b">
@@ -3307,35 +3169,33 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEL-1044</t>
+          <t>SEL-2039</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Artelit Klej Fix2</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7649285435337</v>
+        <v>7891987761138</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>28</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1044.pdf</t>
+          <t>https://selena.com/msds/SEL-2039.pdf</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H71" t="b">
@@ -3348,35 +3208,33 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEL-1053</t>
+          <t>SEL-2041</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Klej Fix2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7659662268714</v>
+        <v>7932569138128</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>20 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>28</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1053.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2041.pdf</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H72" t="b">
@@ -3389,35 +3247,33 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEL-1045</t>
+          <t>SEL-2030</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>7937353461559</v>
+        <v>8073847124972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>21 kg/m3</t>
-        </is>
+      <c r="E73" t="n">
+        <v>28</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1045.pdf</t>
+          <t>https://selena.com/msds/SEL-2030.pdf</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H73" t="b">
@@ -3430,35 +3286,33 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEL-1041</t>
+          <t>SEL-2012</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>7975992297811</v>
+        <v>8186927286505</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+      <c r="E74" t="n">
+        <v>28</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1041.pdf</t>
+          <t>https://selena.com/msds/SEL-2012.pdf</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H74" t="b">
@@ -3471,35 +3325,33 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEL-1028</t>
+          <t>SEL-2071</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8088745651215</v>
+        <v>8574279730643</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+      <c r="E75" t="n">
+        <v>28</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1028.pdf</t>
+          <t>https://selena.com/msds/SEL-2071.pdf</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H75" t="b">
@@ -3512,35 +3364,33 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEL-1017</t>
+          <t>SEL-1002</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8263639919343</v>
+        <v>8581718461680</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+      <c r="E76" t="n">
+        <v>25</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1017.pdf</t>
+          <t>https://selena.com/msds/SEL-1002.pdf</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -3553,35 +3403,33 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEL-1094</t>
+          <t>SEL-2017</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Mousse Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8271954408988</v>
+        <v>8876000680564</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>29 kg/m3</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>28</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1094.pdf</t>
+          <t>https://selena.com/msds/SEL-2017.pdf</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H77" t="b">
@@ -3594,35 +3442,33 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEL-1025</t>
+          <t>SEL-2062</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8498444065138</v>
+        <v>8968221113311</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>23 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>28</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1025.pdf</t>
+          <t>https://selena.com/msds/SEL-2062.pdf</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H78" t="b">
@@ -3635,35 +3481,33 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEL-1040</t>
+          <t>SEL-2037</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Mousse Tytan Professional Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8653589174947</v>
+        <v>8974913206818</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
           <t>FR</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>20 kg/m3</t>
-        </is>
+      <c r="E79" t="n">
+        <v>28</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1040.pdf</t>
+          <t>https://selena.com/msds/SEL-2037.pdf</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H79" t="b">
@@ -3676,35 +3520,33 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEL-1010</t>
+          <t>SEL-2064</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Mousse Artelit Silikon Sanitarny</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>8752167857609</v>
+        <v>9090418529904</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>27 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>28</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1010.pdf</t>
+          <t>https://selena.com/msds/SEL-2064.pdf</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H80" t="b">
@@ -3717,30 +3559,28 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEL-1049</t>
+          <t>SEL-1018</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Mousse Artelit Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>8837124382189</v>
+        <v>9158789111331</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>26 kg/m3</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>25</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1049.pdf</t>
+          <t>https://selena.com/msds/SEL-1018.pdf</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3758,35 +3598,33 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEL-1058</t>
+          <t>SEL-2058</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9081504056920</v>
+        <v>9299038180693</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>28</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1058.pdf</t>
+          <t>https://selena.com/msds/SEL-2058.pdf</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H82" t="b">
@@ -3799,35 +3637,33 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SEL-1074</t>
+          <t>SEL-2078</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9191829276099</v>
+        <v>9418863880088</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
+      <c r="E83" t="n">
+        <v>28</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1074.pdf</t>
+          <t>https://selena.com/msds/SEL-2078.pdf</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H83" t="b">
@@ -3840,35 +3676,33 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SEL-1034</t>
+          <t>SEL-2087</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9319236221700</v>
+        <v>9582594916875</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>28</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1034.pdf</t>
+          <t>https://selena.com/msds/SEL-2087.pdf</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -3881,35 +3715,33 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SEL-1031</t>
+          <t>SEL-2073</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>QUILOSA KLEJ FIX2</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9372306162861</v>
+        <v>9616763618027</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>28</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1031.pdf</t>
+          <t>https://selena.com/msds/SEL-2073.pdf</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -3922,35 +3754,33 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SEL-1076</t>
+          <t>SEL-2040</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Quilosa Silikon Sanitarny</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9403942692974</v>
+        <v>9639993111258</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>28</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1076.pdf</t>
+          <t>https://selena.com/msds/SEL-2040.pdf</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H86" t="b">
@@ -3963,35 +3793,33 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SEL-1032</t>
+          <t>SEL-2075</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL PIANA 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9426646806022</v>
+        <v>9673000607724</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>PL</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+          <t>KZ</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>28</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1032.pdf</t>
+          <t>https://selena.com/msds/SEL-2075.pdf</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H87" t="b">
@@ -4004,30 +3832,28 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SEL-1047</t>
+          <t>SEL-2031</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej Fix2</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9500885725153</v>
+        <v>9849521365811</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
           <t>KZ</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
+      <c r="E88" t="n">
+        <v>28</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1047.pdf</t>
+          <t>https://selena.com/msds/SEL-2031.pdf</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -4045,35 +3871,33 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SEL-1084</t>
+          <t>SEL-1004</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ARTELIT SILIKON SANITARNY</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9758501126444</v>
+        <v>9886971264575</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
           <t>PL</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
+      <c r="E89" t="n">
+        <v>25</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1084.pdf</t>
+          <t>https://selena.com/msds/SEL-1004.pdf</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H89" t="b">
@@ -4086,35 +3910,33 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SEL-1079</t>
+          <t>SEL-2043</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>TYTAN PROFESSIONAL SILIKON SANITARNY</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9851835131072</v>
+        <v>9891607373060</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>28</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1079.pdf</t>
+          <t>https://selena.com/msds/SEL-2043.pdf</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H90" t="b">
@@ -4127,35 +3949,33 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SEL-1073</t>
+          <t>SEL-2025</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>QUILOSA SILIKON SANITARNY</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9890039511679</v>
+        <v>9978197023914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>KZ</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
+          <t>PL</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>28</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-1073.pdf</t>
+          <t>https://selena.com/msds/SEL-2025.pdf</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H91" t="b">

--- a/Selena_Master_Data_FINAL.xlsx
+++ b/Selena_Master_Data_FINAL.xlsx
@@ -478,28 +478,28 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SEL-2048</t>
+          <t>SEL-1000</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1022373185644</v>
+        <v>1566835332485</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2048.pdf</t>
+          <t>https://selena.com/msds/SEL-1000.pdf</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -517,33 +517,33 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SEL-2044</t>
+          <t>SEL-1002</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1092684287836</v>
+        <v>2994926040090</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2044.pdf</t>
+          <t>https://selena.com/msds/SEL-1002.pdf</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H3" t="b">
@@ -556,33 +556,33 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>SEL-2089</t>
+          <t>SEL-1004</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1143805552958</v>
+        <v>9375438373744</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2089.pdf</t>
+          <t>https://selena.com/msds/SEL-1004.pdf</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H4" t="b">
@@ -595,33 +595,33 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SEL-2010</t>
+          <t>SEL-1006</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1204110767442</v>
+        <v>5984514376820</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2010.pdf</t>
+          <t>https://selena.com/msds/SEL-1006.pdf</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H5" t="b">
@@ -634,33 +634,33 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>SEL-2011</t>
+          <t>SEL-1008</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1431313708027</v>
+        <v>4988388359578</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2011.pdf</t>
+          <t>https://selena.com/msds/SEL-1008.pdf</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H6" t="b">
@@ -673,33 +673,33 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SEL-2038</t>
+          <t>SEL-1010</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1490743066339</v>
+        <v>2111212281929</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2038.pdf</t>
+          <t>https://selena.com/msds/SEL-1010.pdf</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H7" t="b">
@@ -712,16 +712,16 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SEL-1016</t>
+          <t>SEL-1012</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1677703171119</v>
+        <v>6217899904404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -733,7 +733,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1016.pdf</t>
+          <t>https://selena.com/msds/SEL-1012.pdf</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -751,33 +751,33 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>SEL-2060</t>
+          <t>SEL-1014</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1724818207492</v>
+        <v>6726448885766</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2060.pdf</t>
+          <t>https://selena.com/msds/SEL-1014.pdf</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H9" t="b">
@@ -790,33 +790,33 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SEL-2085</t>
+          <t>SEL-1016</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1749267817447</v>
+        <v>5680754578052</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2085.pdf</t>
+          <t>https://selena.com/msds/SEL-1016.pdf</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H10" t="b">
@@ -829,33 +829,33 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SEL-2063</t>
+          <t>SEL-1018</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1764984288667</v>
+        <v>3720203329847</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2063.pdf</t>
+          <t>https://selena.com/msds/SEL-1018.pdf</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H11" t="b">
@@ -868,16 +868,16 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SEL-2047</t>
+          <t>SEL-2010</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1791439611947</v>
+        <v>5568553532168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -889,7 +889,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2047.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2010.pdf</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -907,16 +907,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>SEL-1008</t>
+          <t>SEL-2011</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1791623521699</v>
+        <v>2155356418205</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -924,16 +924,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1008.pdf</t>
+          <t>https://selena.com/msds/SEL-2011.pdf</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H13" t="b">
@@ -946,7 +946,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>SEL-2070</t>
+          <t>SEL-2012</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -955,11 +955,11 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1832833357240</v>
+        <v>5557449107777</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -967,12 +967,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2070.pdf</t>
+          <t>https://selena.com/msds/SEL-2012.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H14" t="b">
@@ -985,28 +985,28 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SEL-1000</t>
+          <t>SEL-2013</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1936449043351</v>
+        <v>5316895966439</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1000.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2013.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1024,16 +1024,16 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SEL-1014</t>
+          <t>SEL-2014</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>2097253614102</v>
+        <v>3742388369829</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1041,16 +1041,16 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1014.pdf</t>
+          <t>https://selena.com/msds/SEL-2014.pdf</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H16" t="b">
@@ -1063,20 +1063,20 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>SEL-2068</t>
+          <t>SEL-2015</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2343285886804</v>
+        <v>9258849173192</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2068.pdf</t>
+          <t>https://selena.com/msds/SEL-2015.pdf</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H17" t="b">
@@ -1102,20 +1102,20 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SEL-2021</t>
+          <t>SEL-2016</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2422334086189</v>
+        <v>1196335157919</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -1123,12 +1123,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2021.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2016.pdf</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H18" t="b">
@@ -1141,20 +1141,20 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SEL-2045</t>
+          <t>SEL-2017</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2456811561472</v>
+        <v>1549660764440</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1162,12 +1162,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2045.pdf</t>
+          <t>https://selena.com/msds/SEL-2017.pdf</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H19" t="b">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2460088159013</v>
+        <v>5589144525338</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1219,20 +1219,20 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>SEL-2082</t>
+          <t>SEL-2019</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>2576561330723</v>
+        <v>8952056783141</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2082.pdf</t>
+          <t>https://selena.com/msds/SEL-2019.pdf</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1258,16 +1258,16 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SEL-2034</t>
+          <t>SEL-2020</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>2670068131331</v>
+        <v>8133649473488</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2034.pdf</t>
+          <t>https://selena.com/msds/SEL-2020.pdf</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1297,16 +1297,16 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>SEL-2024</t>
+          <t>SEL-2021</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2684136327243</v>
+        <v>1103460358158</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2024.pdf</t>
+          <t>https://selena.com/msds/SEL-2021.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1336,16 +1336,16 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SEL-2029</t>
+          <t>SEL-2022</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2734724082384</v>
+        <v>5683540147917</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -1357,12 +1357,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2029.pdf</t>
+          <t>https://selena.com/msds/SEL-2022.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1375,7 +1375,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SEL-2076</t>
+          <t>SEL-2023</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1384,7 +1384,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2745092225361</v>
+        <v>9615235218192</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2076.pdf</t>
+          <t>https://selena.com/msds/SEL-2023.pdf</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1414,7 +1414,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SEL-2036</t>
+          <t>SEL-2024</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1423,11 +1423,11 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>3118512000486</v>
+        <v>2317426766374</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1435,12 +1435,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2036.pdf</t>
+          <t>https://selena.com/msds/SEL-2024.pdf</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1453,20 +1453,20 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>SEL-2053</t>
+          <t>SEL-2025</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3197400489411</v>
+        <v>2949050357545</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1474,12 +1474,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2053.pdf</t>
+          <t>https://selena.com/msds/SEL-2025.pdf</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1492,16 +1492,16 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>SEL-2083</t>
+          <t>SEL-2026</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>3337387430454</v>
+        <v>2990734844744</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2083.pdf</t>
+          <t>https://selena.com/msds/SEL-2026.pdf</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SEL-2051</t>
+          <t>SEL-2027</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1540,11 +1540,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>3441744655831</v>
+        <v>9069208405843</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2051.pdf</t>
+          <t>https://selena.com/msds/SEL-2027.pdf</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1570,20 +1570,20 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>SEL-2032</t>
+          <t>SEL-2028</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>3614691233930</v>
+        <v>4655772146290</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -1591,12 +1591,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2032.pdf</t>
+          <t>https://selena.com/msds/SEL-2028.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H30" t="b">
@@ -1609,20 +1609,20 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>SEL-2065</t>
+          <t>SEL-2029</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>3726173435905</v>
+        <v>2569965626701</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2065.pdf</t>
+          <t>https://selena.com/msds/SEL-2029.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -1648,20 +1648,20 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SEL-2057</t>
+          <t>SEL-2030</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3779377392144</v>
+        <v>9985701383099</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2057.pdf</t>
+          <t>https://selena.com/msds/SEL-2030.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1687,20 +1687,20 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SEL-2013</t>
+          <t>SEL-2031</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>3795160531739</v>
+        <v>5196416729763</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2013.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2031.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1726,20 +1726,20 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>SEL-2056</t>
+          <t>SEL-2032</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3925124752011</v>
+        <v>1802899632741</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2056.pdf</t>
+          <t>https://selena.com/msds/SEL-2032.pdf</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -1765,20 +1765,20 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>SEL-2028</t>
+          <t>SEL-2033</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3934611066963</v>
+        <v>6753028111049</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2028.pdf</t>
+          <t>https://selena.com/msds/SEL-2033.pdf</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1804,16 +1804,16 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>SEL-2052</t>
+          <t>SEL-2034</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3989592443173</v>
+        <v>8533884398650</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -1825,12 +1825,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2052.pdf</t>
+          <t>https://selena.com/msds/SEL-2034.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -1843,20 +1843,20 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SEL-2022</t>
+          <t>SEL-2035</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>3989697366878</v>
+        <v>6211073899534</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -1864,12 +1864,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2022.pdf</t>
+          <t>https://selena.com/msds/SEL-2035.pdf</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -1882,16 +1882,16 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SEL-2026</t>
+          <t>SEL-2036</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4102374178177</v>
+        <v>9769784542987</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -1903,12 +1903,12 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2026.pdf</t>
+          <t>https://selena.com/msds/SEL-2036.pdf</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -1921,16 +1921,16 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SEL-2020</t>
+          <t>SEL-2037</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>4380545170318</v>
+        <v>2450112974353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -1942,7 +1942,7 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2020.pdf</t>
+          <t>https://selena.com/msds/SEL-2037.pdf</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1960,7 +1960,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SEL-2080</t>
+          <t>SEL-2038</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1969,11 +1969,11 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>4465563544233</v>
+        <v>1243838531654</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -1981,12 +1981,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2080.pdf</t>
+          <t>https://selena.com/msds/SEL-2038.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H40" t="b">
@@ -1999,16 +1999,16 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SEL-2015</t>
+          <t>SEL-2039</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>4513340336745</v>
+        <v>7400664031629</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -2020,12 +2020,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2015.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2039.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -2038,16 +2038,16 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SEL-2027</t>
+          <t>SEL-2040</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>4573368667749</v>
+        <v>6944802264602</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2027.pdf</t>
+          <t>https://selena.com/msds/SEL-2040.pdf</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2077,20 +2077,20 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>SEL-2042</t>
+          <t>SEL-2041</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>4684061093349</v>
+        <v>1230591513501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2098,12 +2098,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2042.pdf</t>
+          <t>https://selena.com/msds/SEL-2041.pdf</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -2116,16 +2116,16 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>SEL-2067</t>
+          <t>SEL-2042</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4992598590558</v>
+        <v>4749470651030</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -2137,7 +2137,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2067.pdf</t>
+          <t>https://selena.com/msds/SEL-2042.pdf</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2155,20 +2155,20 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>SEL-2033</t>
+          <t>SEL-2043</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5029944637928</v>
+        <v>5327123197532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2033.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2043.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -2194,20 +2194,20 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>SEL-2084</t>
+          <t>SEL-2044</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>5093439265601</v>
+        <v>6427847841811</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2215,12 +2215,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2084.pdf</t>
+          <t>https://selena.com/msds/SEL-2044.pdf</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H46" t="b">
@@ -2233,16 +2233,16 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>SEL-2046</t>
+          <t>SEL-2045</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5137387139033</v>
+        <v>5554714254640</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2046.pdf</t>
+          <t>https://selena.com/msds/SEL-2045.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H47" t="b">
@@ -2272,20 +2272,20 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SEL-2016</t>
+          <t>SEL-2046</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>5213263670202</v>
+        <v>8490943567226</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2293,12 +2293,12 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2016.pdf</t>
+          <t>https://selena.com/msds/SEL-2046.pdf</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H48" t="b">
@@ -2311,20 +2311,20 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>SEL-2077</t>
+          <t>SEL-2047</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5303184181413</v>
+        <v>4904719933178</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2332,12 +2332,12 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2077.pdf</t>
+          <t>https://selena.com/msds/SEL-2047.pdf</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H49" t="b">
@@ -2350,16 +2350,16 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>SEL-2081</t>
+          <t>SEL-2048</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5726340673312</v>
+        <v>5835814896307</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -2371,7 +2371,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2081.pdf</t>
+          <t>https://selena.com/msds/SEL-2048.pdf</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2389,20 +2389,20 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SEL-2055</t>
+          <t>SEL-2049</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>5926862184008</v>
+        <v>1067331036573</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E51" t="n">
@@ -2410,12 +2410,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2055.pdf</t>
+          <t>https://selena.com/msds/SEL-2049.pdf</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H51" t="b">
@@ -2428,16 +2428,16 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>SEL-2019</t>
+          <t>SEL-2050</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>5988931325193</v>
+        <v>9514284645910</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2019.pdf</t>
+          <t>https://selena.com/msds/SEL-2050.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -2467,20 +2467,20 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>SEL-2023</t>
+          <t>SEL-2051</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>6023232068164</v>
+        <v>3050043884105</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2023.pdf</t>
+          <t>https://selena.com/msds/SEL-2051.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H53" t="b">
@@ -2506,20 +2506,20 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>SEL-2050</t>
+          <t>SEL-2052</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>6173511481463</v>
+        <v>9215430246676</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2050.pdf</t>
+          <t>https://selena.com/msds/SEL-2052.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H54" t="b">
@@ -2545,20 +2545,20 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>SEL-2035</t>
+          <t>SEL-2053</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>6262788108202</v>
+        <v>1136031973805</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2035.pdf</t>
+          <t>https://selena.com/msds/SEL-2053.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H55" t="b">
@@ -2584,16 +2584,16 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SEL-2061</t>
+          <t>SEL-2054</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>6311693356798</v>
+        <v>3340641419007</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2061.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2054.pdf</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2623,7 +2623,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SEL-2014</t>
+          <t>SEL-2055</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -2632,11 +2632,11 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>6446862466631</v>
+        <v>5913382371158</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E57" t="n">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2014.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2055.pdf</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2662,20 +2662,20 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>SEL-2072</t>
+          <t>SEL-2056</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>6450486585484</v>
+        <v>5685448258401</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E58" t="n">
@@ -2683,12 +2683,12 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2072.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2056.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H58" t="b">
@@ -2701,20 +2701,20 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>SEL-2066</t>
+          <t>SEL-2057</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>6580952323893</v>
+        <v>3195125652427</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2066.pdf</t>
+          <t>https://selena.com/msds/SEL-2057.pdf</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -2740,20 +2740,20 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>SEL-2059</t>
+          <t>SEL-2058</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>6618629275523</v>
+        <v>7505025821971</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2761,12 +2761,12 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2059.pdf</t>
+          <t>https://selena.com/msds/SEL-2058.pdf</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H60" t="b">
@@ -2779,16 +2779,16 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SEL-2069</t>
+          <t>SEL-2059</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>6672228217380</v>
+        <v>8571767709710</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2800,12 +2800,12 @@
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2069.pdf</t>
+          <t>https://selena.com/msds/SEL-2059.pdf</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H61" t="b">
@@ -2818,16 +2818,16 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SEL-2049</t>
+          <t>SEL-2060</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>6715757390739</v>
+        <v>9857812487029</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2049.pdf</t>
+          <t>https://selena.com/msds/SEL-2060.pdf</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
@@ -2857,16 +2857,16 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>SEL-2086</t>
+          <t>SEL-2061</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6718682523145</v>
+        <v>6952199937048</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2878,12 +2878,12 @@
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2086.pdf</t>
+          <t>https://selena.com/msds/SEL-2061.pdf</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H63" t="b">
@@ -2896,16 +2896,16 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>SEL-1006</t>
+          <t>SEL-2062</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>6762341715348</v>
+        <v>2464717434805</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2913,16 +2913,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1006.pdf</t>
+          <t>https://selena.com/msds/SEL-2062.pdf</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H64" t="b">
@@ -2935,33 +2935,33 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SEL-1012</t>
+          <t>SEL-2063</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>6855268434259</v>
+        <v>4853277110507</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1012.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2063.pdf</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H65" t="b">
@@ -2974,16 +2974,16 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>SEL-2054</t>
+          <t>SEL-2064</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>7292520518128</v>
+        <v>6474753320680</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -2995,12 +2995,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2054.pdf</t>
+          <t>https://selena.com/msds/SEL-2064.pdf</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -3013,16 +3013,16 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SEL-1010</t>
+          <t>SEL-2065</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>7450121326874</v>
+        <v>2160350363282</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3030,16 +3030,16 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1010.pdf</t>
+          <t>https://selena.com/msds/SEL-2065.pdf</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H67" t="b">
@@ -3052,7 +3052,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>SEL-2079</t>
+          <t>SEL-2066</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -3061,7 +3061,7 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>7528580919923</v>
+        <v>5927072229357</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3073,7 +3073,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2079.pdf</t>
+          <t>https://selena.com/msds/SEL-2066.pdf</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3091,20 +3091,20 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>SEL-2074</t>
+          <t>SEL-2067</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>7683489560336</v>
+        <v>8323399627172</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2074.pdf</t>
+          <t>https://selena.com/msds/SEL-2067.pdf</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H69" t="b">
@@ -3130,20 +3130,20 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SEL-2088</t>
+          <t>SEL-2068</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>7856245875389</v>
+        <v>1809087148637</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E70" t="n">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2088.pdf</t>
+          <t>https://selena.com/msds/SEL-2068.pdf</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H70" t="b">
@@ -3169,7 +3169,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>SEL-2039</t>
+          <t>SEL-2069</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -3178,11 +3178,11 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>7891987761138</v>
+        <v>2723130111648</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E71" t="n">
@@ -3190,12 +3190,12 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2039.pdf</t>
+          <t>https://selena.com/msds/SEL-2069.pdf</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H71" t="b">
@@ -3208,20 +3208,20 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SEL-2041</t>
+          <t>SEL-2070</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>7932569138128</v>
+        <v>8446949691121</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2041.pdf</t>
+          <t>https://selena.com/msds/SEL-2070.pdf</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -3247,20 +3247,20 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>SEL-2030</t>
+          <t>SEL-2071</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8073847124972</v>
+        <v>8740893454427</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E73" t="n">
@@ -3268,12 +3268,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2030.pdf</t>
+          <t>https://selena.com/msds/SEL-2071.pdf</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H73" t="b">
@@ -3286,20 +3286,20 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>SEL-2012</t>
+          <t>SEL-2072</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>8186927286505</v>
+        <v>2688118934900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2012.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2072.pdf</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H74" t="b">
@@ -3325,7 +3325,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>SEL-2071</t>
+          <t>SEL-2073</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -3334,11 +3334,11 @@
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8574279730643</v>
+        <v>8464260157531</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3346,12 +3346,12 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2071.pdf</t>
+          <t>https://selena.com/msds/SEL-2073.pdf</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H75" t="b">
@@ -3364,16 +3364,16 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>SEL-1002</t>
+          <t>SEL-2074</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>8581718461680</v>
+        <v>5930030504103</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3381,16 +3381,16 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1002.pdf</t>
+          <t>https://selena.com/msds/SEL-2074.pdf</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -3403,20 +3403,20 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>SEL-2017</t>
+          <t>SEL-2075</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>8876000680564</v>
+        <v>2504852477662</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2017.pdf</t>
+          <t>https://selena.com/msds/SEL-2075.pdf</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H77" t="b">
@@ -3442,7 +3442,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SEL-2062</t>
+          <t>SEL-2076</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3451,11 +3451,11 @@
         </is>
       </c>
       <c r="C78" t="n">
-        <v>8968221113311</v>
+        <v>7603388086981</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E78" t="n">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2062.pdf</t>
+          <t>https://selena.com/msds/SEL-2076.pdf</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H78" t="b">
@@ -3481,20 +3481,20 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>SEL-2037</t>
+          <t>SEL-2077</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>8974913206818</v>
+        <v>5287154460207</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E79" t="n">
@@ -3502,12 +3502,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2037.pdf</t>
+          <t>https://selena.com/msds/SEL-2077.pdf</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H79" t="b">
@@ -3520,20 +3520,20 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>SEL-2064</t>
+          <t>SEL-2078</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>9090418529904</v>
+        <v>5243323466939</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2064.pdf</t>
+          <t>https://selena.com/msds/SEL-2078.pdf</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H80" t="b">
@@ -3559,16 +3559,16 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SEL-1018</t>
+          <t>SEL-2079</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>9158789111331</v>
+        <v>5621404241474</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3576,16 +3576,16 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1018.pdf</t>
+          <t>https://selena.com/msds/SEL-2079.pdf</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H81" t="b">
@@ -3598,16 +3598,16 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SEL-2058</t>
+          <t>SEL-2080</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>9299038180693</v>
+        <v>5055419624749</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3619,12 +3619,12 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2058.pdf</t>
+          <t>https://selena.com/msds/SEL-2080.pdf</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H82" t="b">
@@ -3637,20 +3637,20 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>SEL-2078</t>
+          <t>SEL-2081</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>9418863880088</v>
+        <v>3889017888037</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E83" t="n">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2078.pdf</t>
+          <t>https://selena.com/msds/SEL-2081.pdf</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H83" t="b">
@@ -3676,20 +3676,20 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>SEL-2087</t>
+          <t>SEL-2082</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>9582594916875</v>
+        <v>6476444511735</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3697,12 +3697,12 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2087.pdf</t>
+          <t>https://selena.com/msds/SEL-2082.pdf</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -3715,16 +3715,16 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>SEL-2073</t>
+          <t>SEL-2083</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9616763618027</v>
+        <v>9084000269773</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -3736,12 +3736,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2073.pdf</t>
+          <t>https://selena.com/msds/SEL-2083.pdf</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -3754,20 +3754,20 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>SEL-2040</t>
+          <t>SEL-2084</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9639993111258</v>
+        <v>9497169064800</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2040.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2084.pdf</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3793,20 +3793,20 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>SEL-2075</t>
+          <t>SEL-2085</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>9673000607724</v>
+        <v>1880306093083</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2075.pdf</t>
+          <t>https://selena.com/msds/SEL-2085.pdf</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H87" t="b">
@@ -3832,16 +3832,16 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>SEL-2031</t>
+          <t>SEL-2086</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>9849521365811</v>
+        <v>3043721533278</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -3853,7 +3853,7 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2031.pdf</t>
+          <t>https://selena.com/msds/SEL-2086.pdf</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
@@ -3871,28 +3871,28 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>SEL-1004</t>
+          <t>SEL-2087</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>9886971264575</v>
+        <v>5284960962960</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-1004.pdf</t>
+          <t>https://selena.com/msds/SEL-2087.pdf</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -3910,7 +3910,7 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>SEL-2043</t>
+          <t>SEL-2088</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3919,11 +3919,11 @@
         </is>
       </c>
       <c r="C90" t="n">
-        <v>9891607373060</v>
+        <v>3549807686591</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E90" t="n">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2043.pdf</t>
+          <t>https://selena.com/msds/SEL-2088.pdf</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H90" t="b">
@@ -3949,7 +3949,7 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>SEL-2025</t>
+          <t>SEL-2089</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3958,11 +3958,11 @@
         </is>
       </c>
       <c r="C91" t="n">
-        <v>9978197023914</v>
+        <v>4238586979848</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2025.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2089.pdf</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H91" t="b">

--- a/Selena_Master_Data_FINAL.xlsx
+++ b/Selena_Master_Data_FINAL.xlsx
@@ -483,11 +483,11 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Quilosa Piana 65</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1566835332485</v>
+        <v>9931863904797</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2994926040090</v>
+        <v>7184046578092</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -565,7 +565,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>9375438373744</v>
+        <v>2974969772071</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -600,11 +600,11 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>5984514376820</v>
+        <v>7255464486479</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -643,7 +643,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4988388359578</v>
+        <v>5236601819838</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -678,11 +678,11 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2111212281929</v>
+        <v>1835401038310</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -717,11 +717,11 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Artelit Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>6217899904404</v>
+        <v>5516795735083</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -756,11 +756,11 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Tytan Professional Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>6726448885766</v>
+        <v>5240637117122</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -795,11 +795,11 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Tytan Professional Piana 65</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5680754578052</v>
+        <v>7578248896655</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -834,11 +834,11 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Quilosa Piana 65</t>
+          <t>Artelit Piana 65</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3720203329847</v>
+        <v>3272518903253</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -877,11 +877,11 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>5568553532168</v>
+        <v>7152195300055</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -894,7 +894,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H12" t="b">
@@ -912,11 +912,11 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2155356418205</v>
+        <v>1648236053305</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -951,11 +951,11 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5557449107777</v>
+        <v>6344682226985</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -967,7 +967,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2012.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2012.pdf</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -990,15 +990,15 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5316895966439</v>
+        <v>9837900690062</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2013.pdf</t>
+          <t>https://selena.com/msds/SEL-2013.pdf</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H15" t="b">
@@ -1029,15 +1029,15 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3742388369829</v>
+        <v>4972338655940</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -1068,11 +1068,11 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>9258849173192</v>
+        <v>4171446229360</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -1111,7 +1111,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1196335157919</v>
+        <v>9939516610414</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -1146,15 +1146,15 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1549660764440</v>
+        <v>5352937446586</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -1185,15 +1185,15 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>5589144525338</v>
+        <v>7641657459597</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -1201,12 +1201,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2018.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2018.pdf</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H20" t="b">
@@ -1224,15 +1224,15 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>8952056783141</v>
+        <v>7251665745374</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H21" t="b">
@@ -1263,11 +1263,11 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>8133649473488</v>
+        <v>3391053479413</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H22" t="b">
@@ -1306,11 +1306,11 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1103460358158</v>
+        <v>2906182322287</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -1318,12 +1318,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2021.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2021.pdf</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H23" t="b">
@@ -1341,15 +1341,15 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>5683540147917</v>
+        <v>7803863049942</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -1357,12 +1357,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2022.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2022.pdf</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H24" t="b">
@@ -1380,15 +1380,15 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>9615235218192</v>
+        <v>1902392118306</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -1401,7 +1401,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H25" t="b">
@@ -1419,15 +1419,15 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2317426766374</v>
+        <v>2649483799705</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H26" t="b">
@@ -1462,11 +1462,11 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2949050357545</v>
+        <v>5029983790106</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H27" t="b">
@@ -1497,11 +1497,11 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>2990734844744</v>
+        <v>1020680633612</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -1540,11 +1540,11 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>9069208405843</v>
+        <v>3657429231631</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H29" t="b">
@@ -1575,11 +1575,11 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>4655772146290</v>
+        <v>6306729292067</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -1591,7 +1591,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2028.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2028.pdf</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -1614,11 +1614,11 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2569965626701</v>
+        <v>6801363462397</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2029.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2029.pdf</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H31" t="b">
@@ -1653,15 +1653,15 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>9985701383099</v>
+        <v>9431006780688</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2030.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2030.pdf</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H32" t="b">
@@ -1692,11 +1692,11 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>5196416729763</v>
+        <v>8553095792984</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -1708,12 +1708,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2031.pdf</t>
+          <t>https://selena.com/msds/SEL-2031.pdf</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H33" t="b">
@@ -1731,11 +1731,11 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1802899632741</v>
+        <v>8261430870909</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H34" t="b">
@@ -1770,15 +1770,15 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>6753028111049</v>
+        <v>1650938104485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H35" t="b">
@@ -1809,15 +1809,15 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>8533884398650</v>
+        <v>2333006771293</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E36" t="n">
@@ -1825,12 +1825,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2034.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2034.pdf</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H36" t="b">
@@ -1852,7 +1852,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>6211073899534</v>
+        <v>5956657285554</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -1869,7 +1869,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H37" t="b">
@@ -1887,15 +1887,15 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>9769784542987</v>
+        <v>6275662911872</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E38" t="n">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H38" t="b">
@@ -1926,15 +1926,15 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2450112974353</v>
+        <v>3575693961882</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E39" t="n">
@@ -1947,7 +1947,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H39" t="b">
@@ -1969,7 +1969,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>1243838531654</v>
+        <v>8251623214397</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2038.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2038.pdf</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -2004,15 +2004,15 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>7400664031629</v>
+        <v>6783796336031</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E41" t="n">
@@ -2020,12 +2020,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2039.pdf</t>
+          <t>https://selena.com/msds/SEL-2039.pdf</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H41" t="b">
@@ -2043,15 +2043,15 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>6944802264602</v>
+        <v>9466897544871</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -2064,7 +2064,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H42" t="b">
@@ -2082,15 +2082,15 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>1230591513501</v>
+        <v>5940023404716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E43" t="n">
@@ -2103,7 +2103,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H43" t="b">
@@ -2125,11 +2125,11 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>4749470651030</v>
+        <v>2350060101788</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E44" t="n">
@@ -2142,7 +2142,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H44" t="b">
@@ -2160,15 +2160,15 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>5327123197532</v>
+        <v>5967254023587</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E45" t="n">
@@ -2176,12 +2176,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2043.pdf</t>
+          <t>https://selena.com/msds/SEL-2043.pdf</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H45" t="b">
@@ -2203,11 +2203,11 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6427847841811</v>
+        <v>9433382944592</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E46" t="n">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H46" t="b">
@@ -2238,11 +2238,11 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>5554714254640</v>
+        <v>8212731136998</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2045.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2045.pdf</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H47" t="b">
@@ -2277,15 +2277,15 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>8490943567226</v>
+        <v>1811212632119</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E48" t="n">
@@ -2298,7 +2298,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H48" t="b">
@@ -2316,15 +2316,15 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4904719933178</v>
+        <v>6273360667325</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E49" t="n">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H49" t="b">
@@ -2355,15 +2355,15 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>5835814896307</v>
+        <v>6185953262866</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E50" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H50" t="b">
@@ -2394,11 +2394,11 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>1067331036573</v>
+        <v>3076073505989</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -2433,15 +2433,15 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>9514284645910</v>
+        <v>9609032781936</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E52" t="n">
@@ -2449,12 +2449,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2050.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2050.pdf</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H52" t="b">
@@ -2472,15 +2472,15 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3050043884105</v>
+        <v>6237907473535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -2488,12 +2488,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2051.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2051.pdf</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H53" t="b">
@@ -2511,15 +2511,15 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>9215430246676</v>
+        <v>8662899622531</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E54" t="n">
@@ -2527,12 +2527,12 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2052.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2052.pdf</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H54" t="b">
@@ -2550,15 +2550,15 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>1136031973805</v>
+        <v>6976502664436</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E55" t="n">
@@ -2566,12 +2566,12 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2053.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2053.pdf</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H55" t="b">
@@ -2589,11 +2589,11 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3340641419007</v>
+        <v>5909990427531</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -2628,11 +2628,11 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>5913382371158</v>
+        <v>1144232509617</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -2644,12 +2644,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2055.pdf</t>
+          <t>https://selena.com/msds/SEL-2055.pdf</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H57" t="b">
@@ -2667,11 +2667,11 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>5685448258401</v>
+        <v>9612122608765</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2056.pdf</t>
+          <t>https://selena.com/msds/SEL-2056.pdf</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -2706,15 +2706,15 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3195125652427</v>
+        <v>9457575059594</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E59" t="n">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H59" t="b">
@@ -2745,15 +2745,15 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>7505025821971</v>
+        <v>1608945615480</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E60" t="n">
@@ -2766,7 +2766,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H60" t="b">
@@ -2784,11 +2784,11 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>8571767709710</v>
+        <v>6660337883540</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -2823,15 +2823,15 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>9857812487029</v>
+        <v>1358585173061</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E62" t="n">
@@ -2844,7 +2844,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H62" t="b">
@@ -2862,11 +2862,11 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>6952199937048</v>
+        <v>4460676990096</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -2883,7 +2883,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H63" t="b">
@@ -2901,11 +2901,11 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2464717434805</v>
+        <v>1118752964344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -2922,7 +2922,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H64" t="b">
@@ -2940,11 +2940,11 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>4853277110507</v>
+        <v>8548543601755</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -2956,7 +2956,7 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2063.pdf</t>
+          <t>https://selena.com/msds/SEL-2063.pdf</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2979,15 +2979,15 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>6474753320680</v>
+        <v>2798987588224</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E66" t="n">
@@ -3000,7 +3000,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H66" t="b">
@@ -3018,11 +3018,11 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>2160350363282</v>
+        <v>8820798978127</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -3034,7 +3034,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2065.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2065.pdf</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -3057,11 +3057,11 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>5927072229357</v>
+        <v>1717128708086</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -3096,15 +3096,15 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>8323399627172</v>
+        <v>1007886456557</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E69" t="n">
@@ -3112,12 +3112,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2067.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2067.pdf</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H69" t="b">
@@ -3135,11 +3135,11 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>1809087148637</v>
+        <v>8195909027188</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -3174,11 +3174,11 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2723130111648</v>
+        <v>8069097541818</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -3195,7 +3195,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H71" t="b">
@@ -3213,15 +3213,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>8446949691121</v>
+        <v>4340457110740</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E72" t="n">
@@ -3252,11 +3252,11 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>8740893454427</v>
+        <v>5350378158721</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -3291,15 +3291,15 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>2688118934900</v>
+        <v>4343274450902</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E74" t="n">
@@ -3307,12 +3307,12 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2072.pdf</t>
+          <t>https://selena.com/msds/SEL-2072.pdf</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H74" t="b">
@@ -3330,15 +3330,15 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>8464260157531</v>
+        <v>4342492372290</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E75" t="n">
@@ -3351,7 +3351,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H75" t="b">
@@ -3369,11 +3369,11 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>5930030504103</v>
+        <v>9769521691971</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -3385,12 +3385,12 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2074.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2074.pdf</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H76" t="b">
@@ -3408,15 +3408,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>2504852477662</v>
+        <v>3331295132359</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E77" t="n">
@@ -3424,12 +3424,12 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2075.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2075.pdf</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H77" t="b">
@@ -3447,11 +3447,11 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>7603388086981</v>
+        <v>4982197492303</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -3486,11 +3486,11 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>5287154460207</v>
+        <v>3079630341290</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H79" t="b">
@@ -3525,15 +3525,15 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Artelit Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>5243323466939</v>
+        <v>1116914064998</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E80" t="n">
@@ -3546,7 +3546,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H80" t="b">
@@ -3564,11 +3564,11 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>5621404241474</v>
+        <v>7810015083796</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/SEL-2079.pdf</t>
+          <t>https://selena.com/msds/RECOVERED_SEL-2079.pdf</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3603,11 +3603,11 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>5055419624749</v>
+        <v>4118900358922</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
         </is>
       </c>
       <c r="C83" t="n">
-        <v>3889017888037</v>
+        <v>8352842480200</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -3681,15 +3681,15 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Quilosa Silikon</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>6476444511735</v>
+        <v>4455516230427</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E84" t="n">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H84" t="b">
@@ -3720,15 +3720,15 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Quilosa Klej</t>
+          <t>Tytan Professional Klej</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>9084000269773</v>
+        <v>9245761658309</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>PL</t>
+          <t>KZ</t>
         </is>
       </c>
       <c r="E85" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Kleje</t>
         </is>
       </c>
       <c r="H85" t="b">
@@ -3759,15 +3759,15 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Artelit Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>9497169064800</v>
+        <v>5448681092954</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E86" t="n">
@@ -3775,12 +3775,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2084.pdf</t>
+          <t>https://selena.com/msds/SEL-2084.pdf</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Kleje</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H86" t="b">
@@ -3798,15 +3798,15 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Tytan Professional Klej</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>1880306093083</v>
+        <v>8253395253633</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E87" t="n">
@@ -3819,7 +3819,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H87" t="b">
@@ -3837,15 +3837,15 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Artelit Silikon</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>3043721533278</v>
+        <v>7364474601211</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>KZ</t>
+          <t>FR</t>
         </is>
       </c>
       <c r="E88" t="n">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Piany</t>
+          <t>Unmapped_FR</t>
         </is>
       </c>
       <c r="H88" t="b">
@@ -3876,11 +3876,11 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Tytan Professional Silikon</t>
+          <t>Artelit Klej</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>5284960962960</v>
+        <v>2553892922438</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -3915,11 +3915,11 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Quilosa Klej</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>3549807686591</v>
+        <v>2741448304732</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Uszczelniacze</t>
+          <t>Piany</t>
         </is>
       </c>
       <c r="H90" t="b">
@@ -3954,15 +3954,15 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Quilosa Silikon</t>
+          <t>Tytan Professional Silikon</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>4238586979848</v>
+        <v>6431402736880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>FR</t>
+          <t>PL</t>
         </is>
       </c>
       <c r="E91" t="n">
@@ -3970,12 +3970,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>https://selena.com/msds/RECOVERED_SEL-2089.pdf</t>
+          <t>https://selena.com/msds/SEL-2089.pdf</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Unmapped_FR</t>
+          <t>Uszczelniacze</t>
         </is>
       </c>
       <c r="H91" t="b">
